--- a/healthcare_forms/014_template_covid_19_daily_health_checklist_city_of_fresno--healthcare_forms.xlsx
+++ b/healthcare_forms/014_template_covid_19_daily_health_checklist_city_of_fresno--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sore Throat</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fatigue</t>
+          <t>muscle_or_body_aches</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fatigue</t>
+          <t>Muscle or body aches</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>muscle_or_body_aches</t>
+          <t>diarrhea</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Muscle or body aches</t>
+          <t>Diarrhea</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>diarrhea</t>
+          <t>headache</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Diarrhea</t>
+          <t>Headache</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>headache</t>
+          <t>new_loss_of_taste_or_smell</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Headache</t>
+          <t>New loss of taste or smell</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>new_loss_of_taste_or_smell</t>
+          <t>numbness_or_tingling</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New loss of taste or smell</t>
+          <t>Numbness or tingling</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>numbness_or_tingling</t>
+          <t>confusion</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Numbness or tingling</t>
+          <t>Confusion</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>confusion</t>
+          <t>difficulty_breathing_or_shortness_of_breath</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Confusion</t>
+          <t>Difficulty breathing or shortness of breath</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>difficulty_breathing_or_shortness_of_breath</t>
+          <t>chest_pain_or_discomfort</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Difficulty breathing or shortness of breath</t>
+          <t>Chest pain or discomfort</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>chest_pain_or_discomfort</t>
+          <t>constriction_or_chest_tightness</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chest pain or discomfort</t>
+          <t>Constriction or chest tightness</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>constriction_or_chest_tightness</t>
+          <t>repeated_shaking_or_trembling</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Constriction or chest tightness</t>
+          <t>Repeated shaking or trembling</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>repeated_shaking_or_trembling</t>
+          <t>dizziness_or_feeling_faint</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Repeated shaking or trembling</t>
+          <t>Dizziness or feeling faint</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>confusion</t>
+          <t>nausea_or_vomiting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Confusion</t>
+          <t>Nausea or vomiting</t>
         </is>
       </c>
     </row>
@@ -1454,452 +1454,180 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>dizziness_or_feeling_faint</t>
+          <t>new_loss_of_smell</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dizziness or feeling faint</t>
+          <t>New loss of smell</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>contact_tracing_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>muscle_or_body_aches</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Muscle or body aches</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>contact_tracing_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nausea_or_vomiting</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nausea or vomiting</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>travel_history_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>runny_nose</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Runny nose</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>travel_history_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sore Throat</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>recent_travel_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>headache</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Headache</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>recent_travel_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>fatigue</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fatigue</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>contact_person_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>diarrhea</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Diarrhea</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>contact_person_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>cough</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cough</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>contact_number_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>new_loss_of_taste_or_smell</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New loss of taste or smell</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>contact_number_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>new_loss_of_smell</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
-        <is>
-          <t>New loss of smell</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>symptoms_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>shortness_of_breath</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Shortness of breath</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>symptoms_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>sore_throat</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Sore Throat</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>symptoms_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>chest_pain_or_discomfort</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Chest pain or discomfort</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>symptoms_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>cough</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Cough</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>symptoms_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>new_loss_of_taste_or_smell</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>New loss of taste or smell</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>symptoms_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>repeated_shaking_or_trembling</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Repeated shaking or trembling</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>contact_tracing_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>contact_tracing_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>travel_history_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>travel_history_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>recent_travel_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>recent_travel_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>contact_person_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>contact_person_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>contact_number_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>contact_number_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
         <is>
           <t>False</t>
         </is>
